--- a/root_phene.xlsx
+++ b/root_phene.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xianer_documents\Article\8-水稻一周幼苗动态发育过程分析\Plant Phenomics\Data Availability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C8D5E1-5066-4DBF-8E4C-5A04B698A32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52536A1-8CCD-4F19-A556-0BB1AA9313FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="48" yWindow="2568" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -156,13 +156,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,30 +463,30 @@
       <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="4"/>
+      <c r="M2" s="5"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
@@ -524,10 +524,10 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -565,10 +565,10 @@
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -645,7 +645,7 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0.83</v>
@@ -686,7 +686,7 @@
         <v>1</v>
       </c>
       <c r="K7">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <v>0.74</v>
@@ -765,7 +765,7 @@
         <v>203908.93</v>
       </c>
       <c r="J9">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="K9">
         <v>8</v>
@@ -809,7 +809,7 @@
         <v>7</v>
       </c>
       <c r="K10">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>0.28999999999999998</v>
@@ -847,10 +847,10 @@
         <v>457523.31</v>
       </c>
       <c r="J11">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>0.23</v>
@@ -888,7 +888,7 @@
         <v>646454.06000000006</v>
       </c>
       <c r="J12">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>11</v>
